--- a/inst/extdata/country_name_lookup.xlsx
+++ b/inst/extdata/country_name_lookup.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpeploe\Documents\git_repos\worlddatr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C4A46E-9D70-4B23-8DDB-C6350CC70505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA62FBD-6FFE-4B4A-A2EE-8CC71655DC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="country_name_lookup" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">country_name_lookup!$A$1:$C$599</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">country_name_lookup!$A$1:$C$601</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="1099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="1101">
   <si>
     <t>alpha_3_code</t>
   </si>
@@ -3325,6 +3325,12 @@
   </si>
   <si>
     <t>Cote d´Ivoire</t>
+  </si>
+  <si>
+    <t>Naoero</t>
+  </si>
+  <si>
+    <t>the Republic of Naoero</t>
   </si>
 </sst>
 </file>
@@ -4165,7 +4171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C599"/>
+  <dimension ref="A1:C601"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -8558,150 +8564,150 @@
         <v>483</v>
       </c>
       <c r="C399" t="s">
-        <v>1010</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="B400" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="C400" t="s">
-        <v>497</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>524</v>
+        <v>482</v>
       </c>
       <c r="B401" t="s">
-        <v>525</v>
+        <v>483</v>
       </c>
       <c r="C401" t="s">
-        <v>526</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="B402" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="C402" t="s">
-        <v>1018</v>
+        <v>497</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B403" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C403" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B404" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C404" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="B405" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C405" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="B406" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C406" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="B407" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="C407" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="B408" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="C408" t="s">
-        <v>835</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B409" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C409" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B410" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C410" t="s">
-        <v>1024</v>
+        <v>835</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B411" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C411" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B412" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C412" t="s">
-        <v>551</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -8712,7 +8718,7 @@
         <v>550</v>
       </c>
       <c r="C413" t="s">
-        <v>886</v>
+        <v>552</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -8723,7 +8729,7 @@
         <v>550</v>
       </c>
       <c r="C414" t="s">
-        <v>887</v>
+        <v>551</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -8734,106 +8740,106 @@
         <v>550</v>
       </c>
       <c r="C415" t="s">
-        <v>1025</v>
+        <v>886</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="B416" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="C416" t="s">
-        <v>532</v>
+        <v>887</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="B417" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="C417" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="B418" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C418" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="B419" t="s">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="C419" t="s">
-        <v>558</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="B420" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="C420" t="s">
-        <v>1026</v>
+        <v>542</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B421" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="C421" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B422" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="C422" t="s">
-        <v>565</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>367</v>
+        <v>562</v>
       </c>
       <c r="B423" t="s">
-        <v>368</v>
+        <v>563</v>
       </c>
       <c r="C423" t="s">
-        <v>802</v>
+        <v>564</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>367</v>
+        <v>562</v>
       </c>
       <c r="B424" t="s">
-        <v>368</v>
+        <v>563</v>
       </c>
       <c r="C424" t="s">
-        <v>369</v>
+        <v>565</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -8844,7 +8850,7 @@
         <v>368</v>
       </c>
       <c r="C425" t="s">
-        <v>370</v>
+        <v>802</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -8855,7 +8861,7 @@
         <v>368</v>
       </c>
       <c r="C426" t="s">
-        <v>882</v>
+        <v>369</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -8866,7 +8872,7 @@
         <v>368</v>
       </c>
       <c r="C427" t="s">
-        <v>834</v>
+        <v>370</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -8877,29 +8883,29 @@
         <v>368</v>
       </c>
       <c r="C428" t="s">
-        <v>980</v>
+        <v>882</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>559</v>
+        <v>367</v>
       </c>
       <c r="B429" t="s">
-        <v>560</v>
+        <v>368</v>
       </c>
       <c r="C429" t="s">
-        <v>815</v>
+        <v>834</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>559</v>
+        <v>367</v>
       </c>
       <c r="B430" t="s">
-        <v>560</v>
+        <v>368</v>
       </c>
       <c r="C430" t="s">
-        <v>831</v>
+        <v>980</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -8910,7 +8916,7 @@
         <v>560</v>
       </c>
       <c r="C431" t="s">
-        <v>561</v>
+        <v>815</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -8921,51 +8927,51 @@
         <v>560</v>
       </c>
       <c r="C432" t="s">
-        <v>1027</v>
+        <v>831</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="B433" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="C433" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="B434" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="C434" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="B435" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="C435" t="s">
-        <v>811</v>
+        <v>545</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="B436" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="C436" t="s">
-        <v>535</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -8976,7 +8982,7 @@
         <v>534</v>
       </c>
       <c r="C437" t="s">
-        <v>536</v>
+        <v>811</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -8987,7 +8993,7 @@
         <v>534</v>
       </c>
       <c r="C438" t="s">
-        <v>1092</v>
+        <v>535</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -8998,7 +9004,7 @@
         <v>534</v>
       </c>
       <c r="C439" t="s">
-        <v>1091</v>
+        <v>536</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9009,95 +9015,95 @@
         <v>534</v>
       </c>
       <c r="C440" t="s">
-        <v>1021</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>244</v>
+        <v>533</v>
       </c>
       <c r="B441" t="s">
-        <v>245</v>
+        <v>534</v>
       </c>
       <c r="C441" t="s">
-        <v>246</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>566</v>
+        <v>533</v>
       </c>
       <c r="B442" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="C442" t="s">
-        <v>568</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>566</v>
+        <v>244</v>
       </c>
       <c r="B443" t="s">
-        <v>567</v>
+        <v>245</v>
       </c>
       <c r="C443" t="s">
-        <v>1028</v>
+        <v>246</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="B444" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C444" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="B445" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C445" t="s">
-        <v>888</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="B446" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="C446" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B447" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="C447" t="s">
-        <v>837</v>
+        <v>888</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B448" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C448" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9108,7 +9114,7 @@
         <v>573</v>
       </c>
       <c r="C449" t="s">
-        <v>574</v>
+        <v>837</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9119,7 +9125,7 @@
         <v>573</v>
       </c>
       <c r="C450" t="s">
-        <v>889</v>
+        <v>575</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9130,73 +9136,73 @@
         <v>573</v>
       </c>
       <c r="C451" t="s">
-        <v>1029</v>
+        <v>574</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B452" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C452" t="s">
-        <v>578</v>
+        <v>889</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B453" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C453" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="B454" t="s">
-        <v>617</v>
+        <v>577</v>
       </c>
       <c r="C454" t="s">
-        <v>618</v>
+        <v>578</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="B455" t="s">
-        <v>617</v>
+        <v>577</v>
       </c>
       <c r="C455" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>665</v>
+        <v>616</v>
       </c>
       <c r="B456" t="s">
-        <v>666</v>
+        <v>617</v>
       </c>
       <c r="C456" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>665</v>
+        <v>616</v>
       </c>
       <c r="B457" t="s">
-        <v>666</v>
+        <v>617</v>
       </c>
       <c r="C457" t="s">
-        <v>667</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9207,7 +9213,7 @@
         <v>666</v>
       </c>
       <c r="C458" t="s">
-        <v>894</v>
+        <v>668</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9218,73 +9224,73 @@
         <v>666</v>
       </c>
       <c r="C459" t="s">
-        <v>1047</v>
+        <v>667</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>619</v>
+        <v>665</v>
       </c>
       <c r="B460" t="s">
-        <v>620</v>
+        <v>666</v>
       </c>
       <c r="C460" t="s">
-        <v>621</v>
+        <v>894</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>619</v>
+        <v>665</v>
       </c>
       <c r="B461" t="s">
-        <v>620</v>
+        <v>666</v>
       </c>
       <c r="C461" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B462" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="C462" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="B463" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="C463" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="B464" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="C464" t="s">
-        <v>845</v>
+        <v>633</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="B465" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="C465" t="s">
-        <v>655</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9295,29 +9301,29 @@
         <v>654</v>
       </c>
       <c r="C466" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>585</v>
+        <v>653</v>
       </c>
       <c r="B467" t="s">
-        <v>586</v>
+        <v>654</v>
       </c>
       <c r="C467" t="s">
-        <v>890</v>
+        <v>655</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>585</v>
+        <v>653</v>
       </c>
       <c r="B468" t="s">
-        <v>586</v>
+        <v>654</v>
       </c>
       <c r="C468" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9328,194 +9334,194 @@
         <v>586</v>
       </c>
       <c r="C469" t="s">
-        <v>587</v>
+        <v>890</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>672</v>
+        <v>585</v>
       </c>
       <c r="B470" t="s">
-        <v>673</v>
+        <v>586</v>
       </c>
       <c r="C470" t="s">
-        <v>674</v>
+        <v>839</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>644</v>
+        <v>585</v>
       </c>
       <c r="B471" t="s">
-        <v>645</v>
+        <v>586</v>
       </c>
       <c r="C471" t="s">
-        <v>646</v>
+        <v>587</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="B472" t="s">
-        <v>629</v>
+        <v>673</v>
       </c>
       <c r="C472" t="s">
-        <v>630</v>
+        <v>674</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="B473" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="C473" t="s">
-        <v>1038</v>
+        <v>646</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>207</v>
+        <v>628</v>
       </c>
       <c r="B474" t="s">
-        <v>208</v>
+        <v>629</v>
       </c>
       <c r="C474" t="s">
-        <v>209</v>
+        <v>630</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>207</v>
+        <v>628</v>
       </c>
       <c r="B475" t="s">
-        <v>208</v>
+        <v>629</v>
       </c>
       <c r="C475" t="s">
-        <v>949</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>610</v>
+        <v>207</v>
       </c>
       <c r="B476" t="s">
-        <v>611</v>
+        <v>208</v>
       </c>
       <c r="C476" t="s">
-        <v>612</v>
+        <v>209</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>610</v>
+        <v>207</v>
       </c>
       <c r="B477" t="s">
-        <v>611</v>
+        <v>208</v>
       </c>
       <c r="C477" t="s">
-        <v>1032</v>
+        <v>949</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>647</v>
+        <v>610</v>
       </c>
       <c r="B478" t="s">
-        <v>648</v>
+        <v>611</v>
       </c>
       <c r="C478" t="s">
-        <v>649</v>
+        <v>612</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>647</v>
+        <v>610</v>
       </c>
       <c r="B479" t="s">
-        <v>648</v>
+        <v>611</v>
       </c>
       <c r="C479" t="s">
-        <v>1042</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="B480" t="s">
-        <v>601</v>
+        <v>648</v>
       </c>
       <c r="C480" t="s">
-        <v>602</v>
+        <v>649</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="B481" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="C481" t="s">
-        <v>624</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="B482" t="s">
-        <v>623</v>
+        <v>601</v>
       </c>
       <c r="C482" t="s">
-        <v>1036</v>
+        <v>602</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>656</v>
+        <v>622</v>
       </c>
       <c r="B483" t="s">
-        <v>657</v>
+        <v>623</v>
       </c>
       <c r="C483" t="s">
-        <v>658</v>
+        <v>624</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>656</v>
+        <v>622</v>
       </c>
       <c r="B484" t="s">
-        <v>657</v>
+        <v>623</v>
       </c>
       <c r="C484" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>613</v>
+        <v>656</v>
       </c>
       <c r="B485" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="C485" t="s">
-        <v>615</v>
+        <v>658</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>613</v>
+        <v>656</v>
       </c>
       <c r="B486" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="C486" t="s">
-        <v>799</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -9526,51 +9532,51 @@
         <v>614</v>
       </c>
       <c r="C487" t="s">
-        <v>1033</v>
+        <v>615</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>669</v>
+        <v>613</v>
       </c>
       <c r="B488" t="s">
-        <v>670</v>
+        <v>614</v>
       </c>
       <c r="C488" t="s">
-        <v>671</v>
+        <v>799</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>669</v>
+        <v>613</v>
       </c>
       <c r="B489" t="s">
-        <v>670</v>
+        <v>614</v>
       </c>
       <c r="C489" t="s">
-        <v>1048</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="B490" t="s">
-        <v>638</v>
+        <v>670</v>
       </c>
       <c r="C490" t="s">
-        <v>640</v>
+        <v>671</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="B491" t="s">
-        <v>638</v>
+        <v>670</v>
       </c>
       <c r="C491" t="s">
-        <v>639</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -9581,73 +9587,73 @@
         <v>638</v>
       </c>
       <c r="C492" t="s">
-        <v>1040</v>
+        <v>640</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B493" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C493" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B494" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C494" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="B495" t="s">
-        <v>676</v>
+        <v>642</v>
       </c>
       <c r="C495" t="s">
-        <v>677</v>
+        <v>643</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="B496" t="s">
-        <v>676</v>
+        <v>642</v>
       </c>
       <c r="C496" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>219</v>
+        <v>675</v>
       </c>
       <c r="B497" t="s">
-        <v>220</v>
+        <v>676</v>
       </c>
       <c r="C497" t="s">
-        <v>221</v>
+        <v>677</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>219</v>
+        <v>675</v>
       </c>
       <c r="B498" t="s">
-        <v>220</v>
+        <v>676</v>
       </c>
       <c r="C498" t="s">
-        <v>848</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -9658,73 +9664,73 @@
         <v>220</v>
       </c>
       <c r="C499" t="s">
-        <v>953</v>
+        <v>221</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>634</v>
+        <v>219</v>
       </c>
       <c r="B500" t="s">
-        <v>635</v>
+        <v>220</v>
       </c>
       <c r="C500" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>634</v>
+        <v>219</v>
       </c>
       <c r="B501" t="s">
-        <v>635</v>
+        <v>220</v>
       </c>
       <c r="C501" t="s">
-        <v>636</v>
+        <v>953</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="B502" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="C502" t="s">
-        <v>627</v>
+        <v>844</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="B503" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="C503" t="s">
-        <v>1037</v>
+        <v>636</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>681</v>
+        <v>625</v>
       </c>
       <c r="B504" t="s">
-        <v>682</v>
+        <v>626</v>
       </c>
       <c r="C504" t="s">
-        <v>849</v>
+        <v>627</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>681</v>
+        <v>625</v>
       </c>
       <c r="B505" t="s">
-        <v>682</v>
+        <v>626</v>
       </c>
       <c r="C505" t="s">
-        <v>684</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -9735,7 +9741,7 @@
         <v>682</v>
       </c>
       <c r="C506" t="s">
-        <v>683</v>
+        <v>849</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -9746,7 +9752,7 @@
         <v>682</v>
       </c>
       <c r="C507" t="s">
-        <v>895</v>
+        <v>684</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -9757,29 +9763,29 @@
         <v>682</v>
       </c>
       <c r="C508" t="s">
-        <v>1051</v>
+        <v>683</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>720</v>
+        <v>681</v>
       </c>
       <c r="B509" t="s">
-        <v>721</v>
+        <v>682</v>
       </c>
       <c r="C509" t="s">
-        <v>723</v>
+        <v>895</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>720</v>
+        <v>681</v>
       </c>
       <c r="B510" t="s">
-        <v>721</v>
+        <v>682</v>
       </c>
       <c r="C510" t="s">
-        <v>722</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -9790,139 +9796,139 @@
         <v>721</v>
       </c>
       <c r="C511" t="s">
-        <v>897</v>
+        <v>723</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>133</v>
+        <v>720</v>
       </c>
       <c r="B512" t="s">
-        <v>134</v>
+        <v>721</v>
       </c>
       <c r="C512" t="s">
-        <v>135</v>
+        <v>722</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>133</v>
+        <v>720</v>
       </c>
       <c r="B513" t="s">
-        <v>134</v>
+        <v>721</v>
       </c>
       <c r="C513" t="s">
-        <v>930</v>
+        <v>897</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>702</v>
+        <v>133</v>
       </c>
       <c r="B514" t="s">
-        <v>703</v>
+        <v>134</v>
       </c>
       <c r="C514" t="s">
-        <v>704</v>
+        <v>135</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>702</v>
+        <v>133</v>
       </c>
       <c r="B515" t="s">
-        <v>703</v>
+        <v>134</v>
       </c>
       <c r="C515" t="s">
-        <v>1056</v>
+        <v>930</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="B516" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C516" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="B517" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C517" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B518" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="C518" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B519" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="C519" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="B520" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="C520" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>717</v>
+        <v>689</v>
       </c>
       <c r="B521" t="s">
-        <v>718</v>
+        <v>690</v>
       </c>
       <c r="C521" t="s">
-        <v>719</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B522" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="C522" t="s">
-        <v>896</v>
+        <v>707</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>699</v>
+        <v>717</v>
       </c>
       <c r="B523" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
       <c r="C523" t="s">
-        <v>1094</v>
+        <v>719</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -9933,7 +9939,7 @@
         <v>700</v>
       </c>
       <c r="C524" t="s">
-        <v>701</v>
+        <v>896</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -9944,51 +9950,51 @@
         <v>700</v>
       </c>
       <c r="C525" t="s">
-        <v>1055</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="B526" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="C526" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="B527" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="C527" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B528" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C528" t="s">
-        <v>851</v>
+        <v>710</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B529" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C529" t="s">
-        <v>852</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -9999,7 +10005,7 @@
         <v>712</v>
       </c>
       <c r="C530" t="s">
-        <v>713</v>
+        <v>851</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10010,51 +10016,51 @@
         <v>712</v>
       </c>
       <c r="C531" t="s">
-        <v>1058</v>
+        <v>852</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B532" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C532" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B533" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C533" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="B534" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="C534" t="s">
-        <v>853</v>
+        <v>716</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="B535" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="C535" t="s">
-        <v>729</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10065,7 +10071,7 @@
         <v>728</v>
       </c>
       <c r="C536" t="s">
-        <v>800</v>
+        <v>853</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10076,40 +10082,40 @@
         <v>728</v>
       </c>
       <c r="C537" t="s">
-        <v>1060</v>
+        <v>729</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B538" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C538" t="s">
-        <v>726</v>
+        <v>800</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>685</v>
+        <v>727</v>
       </c>
       <c r="B539" t="s">
-        <v>686</v>
+        <v>728</v>
       </c>
       <c r="C539" t="s">
-        <v>850</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="B540" t="s">
-        <v>686</v>
+        <v>725</v>
       </c>
       <c r="C540" t="s">
-        <v>687</v>
+        <v>726</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10120,29 +10126,29 @@
         <v>686</v>
       </c>
       <c r="C541" t="s">
-        <v>688</v>
+        <v>850</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="B542" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="C542" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="B543" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="C543" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10153,7 +10159,7 @@
         <v>693</v>
       </c>
       <c r="C544" t="s">
-        <v>805</v>
+        <v>695</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10164,95 +10170,95 @@
         <v>693</v>
       </c>
       <c r="C545" t="s">
-        <v>1053</v>
+        <v>694</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>730</v>
+        <v>692</v>
       </c>
       <c r="B546" t="s">
-        <v>731</v>
+        <v>693</v>
       </c>
       <c r="C546" t="s">
-        <v>732</v>
+        <v>805</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>730</v>
+        <v>692</v>
       </c>
       <c r="B547" t="s">
-        <v>731</v>
+        <v>693</v>
       </c>
       <c r="C547" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B548" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C548" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="B549" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="C549" t="s">
-        <v>746</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
       <c r="B550" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="C550" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="B551" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="C551" t="s">
-        <v>1065</v>
+        <v>746</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B552" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C552" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B553" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C553" t="s">
-        <v>748</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10263,7 +10269,7 @@
         <v>748</v>
       </c>
       <c r="C554" t="s">
-        <v>1077</v>
+        <v>750</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10274,7 +10280,7 @@
         <v>748</v>
       </c>
       <c r="C555" t="s">
-        <v>1078</v>
+        <v>748</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10285,7 +10291,7 @@
         <v>748</v>
       </c>
       <c r="C556" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10296,7 +10302,7 @@
         <v>748</v>
       </c>
       <c r="C557" t="s">
-        <v>812</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10307,7 +10313,7 @@
         <v>748</v>
       </c>
       <c r="C558" t="s">
-        <v>749</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10318,7 +10324,7 @@
         <v>748</v>
       </c>
       <c r="C559" t="s">
-        <v>747</v>
+        <v>812</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10329,51 +10335,51 @@
         <v>748</v>
       </c>
       <c r="C560" t="s">
-        <v>1064</v>
+        <v>749</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="B561" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="C561" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="B562" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="C562" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>305</v>
+        <v>754</v>
       </c>
       <c r="B563" t="s">
-        <v>306</v>
+        <v>755</v>
       </c>
       <c r="C563" t="s">
-        <v>875</v>
+        <v>756</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>305</v>
+        <v>754</v>
       </c>
       <c r="B564" t="s">
-        <v>306</v>
+        <v>755</v>
       </c>
       <c r="C564" t="s">
-        <v>307</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10384,7 +10390,7 @@
         <v>306</v>
       </c>
       <c r="C565" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10395,29 +10401,29 @@
         <v>306</v>
       </c>
       <c r="C566" t="s">
-        <v>855</v>
+        <v>307</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>603</v>
+        <v>305</v>
       </c>
       <c r="B567" t="s">
-        <v>604</v>
+        <v>306</v>
       </c>
       <c r="C567" t="s">
-        <v>826</v>
+        <v>874</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>603</v>
+        <v>305</v>
       </c>
       <c r="B568" t="s">
-        <v>604</v>
+        <v>306</v>
       </c>
       <c r="C568" t="s">
-        <v>842</v>
+        <v>855</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10428,7 +10434,7 @@
         <v>604</v>
       </c>
       <c r="C569" t="s">
-        <v>605</v>
+        <v>826</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10439,29 +10445,29 @@
         <v>604</v>
       </c>
       <c r="C570" t="s">
-        <v>606</v>
+        <v>842</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>760</v>
+        <v>603</v>
       </c>
       <c r="B571" t="s">
-        <v>761</v>
+        <v>604</v>
       </c>
       <c r="C571" t="s">
-        <v>856</v>
+        <v>605</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>760</v>
+        <v>603</v>
       </c>
       <c r="B572" t="s">
-        <v>761</v>
+        <v>604</v>
       </c>
       <c r="C572" t="s">
-        <v>762</v>
+        <v>606</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10472,7 +10478,7 @@
         <v>761</v>
       </c>
       <c r="C573" t="s">
-        <v>763</v>
+        <v>856</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -10483,29 +10489,29 @@
         <v>761</v>
       </c>
       <c r="C574" t="s">
-        <v>1068</v>
+        <v>762</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="B575" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="C575" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="B576" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="C576" t="s">
-        <v>770</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -10516,29 +10522,29 @@
         <v>769</v>
       </c>
       <c r="C577" t="s">
-        <v>1070</v>
+        <v>771</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B578" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C578" t="s">
-        <v>809</v>
+        <v>770</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B579" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C579" t="s">
-        <v>774</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -10549,29 +10555,29 @@
         <v>773</v>
       </c>
       <c r="C580" t="s">
-        <v>1071</v>
+        <v>809</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="B581" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="C581" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="B582" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="C582" t="s">
-        <v>767</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -10582,106 +10588,106 @@
         <v>765</v>
       </c>
       <c r="C583" t="s">
-        <v>1069</v>
+        <v>766</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="B584" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="C584" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="B585" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="C585" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="B586" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="C586" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="B587" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="C587" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>607</v>
+        <v>775</v>
       </c>
       <c r="B588" t="s">
-        <v>608</v>
+        <v>776</v>
       </c>
       <c r="C588" t="s">
-        <v>609</v>
+        <v>777</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>607</v>
+        <v>775</v>
       </c>
       <c r="B589" t="s">
-        <v>608</v>
+        <v>776</v>
       </c>
       <c r="C589" t="s">
-        <v>1031</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>794</v>
+        <v>607</v>
       </c>
       <c r="B590" t="s">
-        <v>795</v>
+        <v>608</v>
       </c>
       <c r="C590" t="s">
-        <v>796</v>
+        <v>609</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>781</v>
+        <v>607</v>
       </c>
       <c r="B591" t="s">
-        <v>782</v>
+        <v>608</v>
       </c>
       <c r="C591" t="s">
-        <v>783</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="B592" t="s">
-        <v>782</v>
+        <v>795</v>
       </c>
       <c r="C592" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -10692,77 +10698,99 @@
         <v>782</v>
       </c>
       <c r="C593" t="s">
-        <v>1073</v>
+        <v>783</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>650</v>
+        <v>781</v>
       </c>
       <c r="B594" t="s">
-        <v>651</v>
+        <v>782</v>
       </c>
       <c r="C594" t="s">
-        <v>652</v>
+        <v>784</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>650</v>
+        <v>781</v>
       </c>
       <c r="B595" t="s">
-        <v>651</v>
+        <v>782</v>
       </c>
       <c r="C595" t="s">
-        <v>1043</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>785</v>
+        <v>650</v>
       </c>
       <c r="B596" t="s">
-        <v>786</v>
+        <v>651</v>
       </c>
       <c r="C596" t="s">
-        <v>787</v>
+        <v>652</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>785</v>
+        <v>650</v>
       </c>
       <c r="B597" t="s">
-        <v>786</v>
+        <v>651</v>
       </c>
       <c r="C597" t="s">
-        <v>1074</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B598" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C598" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
+        <v>785</v>
+      </c>
+      <c r="B599" t="s">
+        <v>786</v>
+      </c>
+      <c r="C599" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
         <v>788</v>
       </c>
-      <c r="B599" t="s">
+      <c r="B600" t="s">
         <v>789</v>
       </c>
-      <c r="C599" t="s">
+      <c r="C600" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>788</v>
+      </c>
+      <c r="B601" t="s">
+        <v>789</v>
+      </c>
+      <c r="C601" t="s">
         <v>1075</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C412">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C414">
     <sortCondition ref="C1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
